--- a/docs/data/jp/xlsx/9697.xlsx
+++ b/docs/data/jp/xlsx/9697.xlsx
@@ -7344,7 +7344,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Gain On Liquidation Of Subsidiaries And Associates General NOI</t>
+          <t>관계회사 정리이익</t>
         </is>
       </c>
       <c r="T98" s="20" t="n">
@@ -7531,7 +7531,7 @@
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>Litigation Expenses NOE</t>
+          <t>소송 관련 비용</t>
         </is>
       </c>
       <c r="D102" s="20" t="n">
@@ -7553,7 +7553,7 @@
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>Commission For Purchase Of Treasury Stock NOE</t>
+          <t>자기주식 취득비용</t>
         </is>
       </c>
       <c r="D103" s="20" t="n">
@@ -7575,7 +7575,7 @@
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>Social Contribution NOE</t>
+          <t>사회공헌 관련 비용</t>
         </is>
       </c>
       <c r="C104" s="20" t="n">
@@ -7646,7 +7646,7 @@
     <row r="106">
       <c r="A106" s="18" t="inlineStr">
         <is>
-          <t>Social Contribution Activity Related Expenses NOE</t>
+          <t>사회공헌 관련 비용</t>
         </is>
       </c>
       <c r="F106" s="20" t="n">
@@ -9679,7 +9679,7 @@
     <row r="147">
       <c r="A147" s="18" t="inlineStr">
         <is>
-          <t>DegitalContentsReportableSegmentMember · Transactions With Other Segments</t>
+          <t>DegitalContentsReportableSegmentMember · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C147" s="20" t="n">
@@ -9731,7 +9731,7 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>ArcadeOperationsReportableSegmentMember · Transactions With Other Segments</t>
+          <t>ArcadeOperationsReportableSegmentMember · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C148" s="20" t="n">
@@ -9783,7 +9783,7 @@
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>AmusementEquipmentsReportableSegmentMember · Transactions With Other Segments</t>
+          <t>AmusementEquipmentsReportableSegmentMember · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C149" s="20" t="n">
@@ -9835,7 +9835,7 @@
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · Transactions With Other Segments</t>
+          <t>보고부문 합계 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C150" s="20" t="n">
@@ -9887,7 +9887,7 @@
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>기타 · Transactions With Other Segments</t>
+          <t>기타 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C151" s="20" t="n">
@@ -9939,7 +9939,7 @@
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>합계 · Transactions With Other Segments</t>
+          <t>합계 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C152" s="20" t="n">
@@ -9991,7 +9991,7 @@
     <row r="153">
       <c r="A153" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Transactions With Other Segments</t>
+          <t>조정액 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C153" s="20" t="n">
@@ -10077,7 +10077,7 @@
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · Transactions With Other Segments</t>
+          <t>EntityTotalMember · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="F155" s="20" t="n">
@@ -10507,7 +10507,7 @@
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>DegitalContentsReportableSegmentMember · Operating Income</t>
+          <t>DegitalContentsReportableSegmentMember · 부문 손익</t>
         </is>
       </c>
       <c r="C165" s="20" t="n">
@@ -10559,7 +10559,7 @@
     <row r="166">
       <c r="A166" s="18" t="inlineStr">
         <is>
-          <t>ArcadeOperationsReportableSegmentMember · Operating Income</t>
+          <t>ArcadeOperationsReportableSegmentMember · 부문 손익</t>
         </is>
       </c>
       <c r="C166" s="20" t="n">
@@ -10611,7 +10611,7 @@
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>AmusementEquipmentsReportableSegmentMember · Operating Income</t>
+          <t>AmusementEquipmentsReportableSegmentMember · 부문 손익</t>
         </is>
       </c>
       <c r="C167" s="20" t="n">
@@ -10663,7 +10663,7 @@
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · Operating Income</t>
+          <t>보고부문 합계 · 부문 손익</t>
         </is>
       </c>
       <c r="C168" s="20" t="n">
@@ -10715,7 +10715,7 @@
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>기타 · Operating Income</t>
+          <t>기타 · 부문 손익</t>
         </is>
       </c>
       <c r="C169" s="20" t="n">
@@ -10767,7 +10767,7 @@
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>합계 · Operating Income</t>
+          <t>합계 · 부문 손익</t>
         </is>
       </c>
       <c r="C170" s="20" t="n">
@@ -10819,7 +10819,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Operating Income</t>
+          <t>조정액 · 부문 손익</t>
         </is>
       </c>
       <c r="C171" s="20" t="n">
@@ -10871,7 +10871,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>부문 손익</t>
         </is>
       </c>
       <c r="C172" s="12" t="n">
@@ -10905,7 +10905,7 @@
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · Operating Income</t>
+          <t>EntityTotalMember · 부문 손익</t>
         </is>
       </c>
       <c r="F173" s="20" t="n">
@@ -12096,7 +12096,7 @@
     <row r="194">
       <c r="A194" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Media Assets Ope CF</t>
+          <t>영상자산 증감액</t>
         </is>
       </c>
       <c r="I194" s="20" t="n">
@@ -12121,7 +12121,7 @@
     <row r="195">
       <c r="A195" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Work In Progress For Game Software Ope CF</t>
+          <t>게임소프트 재공품 증감액</t>
         </is>
       </c>
       <c r="C195" s="20" t="n">
@@ -12267,7 +12267,7 @@
     <row r="197">
       <c r="A197" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Deferred Income Ope CF</t>
+          <t>이연수익 증감액</t>
         </is>
       </c>
       <c r="C197" s="20" t="n">
@@ -17063,7 +17063,7 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>Media Assets CA</t>
+          <t>영상자산</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
@@ -17119,7 +17119,7 @@
     <row r="79">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>Work In Progress For Game Software CA</t>
+          <t>게임소프트 재공품</t>
         </is>
       </c>
       <c r="C79" s="20" t="n">
@@ -17354,7 +17354,7 @@
     <row r="86">
       <c r="A86" s="18" t="inlineStr">
         <is>
-          <t>Equipment For Amusement Facility Net PPE</t>
+          <t>오락시설 기기(순액)</t>
         </is>
       </c>
       <c r="F86" s="20" t="n">
@@ -18058,7 +18058,7 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>Deferred Revenue CL</t>
+          <t>이연수익</t>
         </is>
       </c>
       <c r="C109" s="20" t="n">
